--- a/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
+++ b/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naveen.natarajan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naveen.natarajan\Downloads\DAQEAI_Codebase_Apr2026\DAQEAI_Codebase_Apr2026\datf_core\test\testprotocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263D536B-9CD5-48A4-A82D-342E6D5B2F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD831D8-B6C9-4A63-961C-E1C66F165C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,10 +273,10 @@
     <t>test/data/source</t>
   </si>
   <si>
-    <t>test_DATF</t>
-  </si>
-  <si>
     <t>testcase1</t>
+  </si>
+  <si>
+    <t>test_DAQE</t>
   </si>
 </sst>
 </file>
@@ -772,7 +772,7 @@
         <v>66</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -812,7 +812,7 @@
         <v>75</v>
       </c>
       <c r="B6" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>7</v>

--- a/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
+++ b/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naveen.natarajan\Downloads\DAQEAI_Codebase_Apr2026\DAQEAI_Codebase_Apr2026\datf_core\test\testprotocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD831D8-B6C9-4A63-961C-E1C66F165C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F812B7-9D09-42B4-A42C-265053F7AD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -267,9 +267,6 @@
     <t>,</t>
   </si>
   <si>
-    <t>source_data.csv</t>
-  </si>
-  <si>
     <t>test/data/source</t>
   </si>
   <si>
@@ -277,6 +274,9 @@
   </si>
   <si>
     <t>test_DAQE</t>
+  </si>
+  <si>
+    <t>source_data</t>
   </si>
 </sst>
 </file>
@@ -772,7 +772,7 @@
         <v>66</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>7</v>
@@ -1003,10 +1003,10 @@
         <v>15</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>7</v>

--- a/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
+++ b/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naveen.natarajan\Downloads\DAQEAI_Codebase_Apr2026\DAQEAI_Codebase_Apr2026\datf_core\test\testprotocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F812B7-9D09-42B4-A42C-265053F7AD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA7336B-43D0-4E42-8116-DB08A9412160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="85">
   <si>
     <t>comparetype</t>
   </si>
@@ -267,23 +267,26 @@
     <t>,</t>
   </si>
   <si>
-    <t>test/data/source</t>
-  </si>
-  <si>
-    <t>testcase1</t>
-  </si>
-  <si>
-    <t>test_DAQE</t>
-  </si>
-  <si>
-    <t>source_data</t>
+    <t>dbfs:/databricks-datasets/sfo_customer_survey/2013_SFO_Customer_Survey.csv</t>
+  </si>
+  <si>
+    <t>2013_SFO_Customer_Survey</t>
+  </si>
+  <si>
+    <t>testDATF</t>
+  </si>
+  <si>
+    <t>testcase1_file_vs_table_comparison</t>
+  </si>
+  <si>
+    <t>source</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,14 +313,6 @@
       <color rgb="FF44546A"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -388,11 +383,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -437,12 +431,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -866,7 +856,7 @@
     <col min="36" max="36" width="15.1796875" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -981,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>7</v>
@@ -992,7 +982,9 @@
       <c r="E2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="8"/>
+      <c r="F2" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="G2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1002,11 +994,11 @@
       <c r="I2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="8" t="s">
         <v>80</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>7</v>
@@ -1050,16 +1042,13 @@
         <v>78</v>
       </c>
       <c r="AI2" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ2" s="10">
-        <v>2000</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" display="/Users/srinath.kolli@tigeranalytics.com/daqe_project/datf_core/test/data/source" xr:uid="{124868A4-3FDB-42A9-BBC2-1C487B2090BC}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
+++ b/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naveen.natarajan\Downloads\DAQEAI_Codebase_Apr2026\DAQEAI_Codebase_Apr2026\datf_core\test\testprotocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA7336B-43D0-4E42-8116-DB08A9412160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE1F931-C446-421A-9100-8C77F0EF4047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -267,9 +267,6 @@
     <t>,</t>
   </si>
   <si>
-    <t>dbfs:/databricks-datasets/sfo_customer_survey/2013_SFO_Customer_Survey.csv</t>
-  </si>
-  <si>
     <t>2013_SFO_Customer_Survey</t>
   </si>
   <si>
@@ -280,6 +277,9 @@
   </si>
   <si>
     <t>source</t>
+  </si>
+  <si>
+    <t>dbfs:/databricks-datasets/sfo_customer_survey/</t>
   </si>
 </sst>
 </file>
@@ -762,7 +762,7 @@
         <v>66</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -971,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>7</v>
@@ -983,7 +983,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>9</v>
@@ -995,10 +995,10 @@
         <v>15</v>
       </c>
       <c r="J2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>7</v>

--- a/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
+++ b/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naveen.natarajan\Downloads\DAQEAI_Codebase_Apr2026\DAQEAI_Codebase_Apr2026\datf_core\test\testprotocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE1F931-C446-421A-9100-8C77F0EF4047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CFA001-30D5-4E6C-AF44-7B51BFCA6877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -267,9 +267,6 @@
     <t>,</t>
   </si>
   <si>
-    <t>2013_SFO_Customer_Survey</t>
-  </si>
-  <si>
     <t>testDATF</t>
   </si>
   <si>
@@ -280,6 +277,9 @@
   </si>
   <si>
     <t>dbfs:/databricks-datasets/sfo_customer_survey/</t>
+  </si>
+  <si>
+    <t>2013_SFO_Customer_Survey.CSV</t>
   </si>
 </sst>
 </file>
@@ -762,7 +762,7 @@
         <v>66</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -971,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>7</v>
@@ -983,7 +983,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>9</v>
@@ -995,10 +995,10 @@
         <v>15</v>
       </c>
       <c r="J2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>84</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>7</v>

--- a/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
+++ b/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/testDATF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naveen.natarajan\Downloads\DAQEAI_Codebase_Apr2026\DAQEAI_Codebase_Apr2026\datf_core\test\testprotocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CFA001-30D5-4E6C-AF44-7B51BFCA6877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74978C0-74DC-41B5-9A98-80E1F9C44E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -267,6 +267,9 @@
     <t>,</t>
   </si>
   <si>
+    <t>2013_SFO_Customer_Survey.csv</t>
+  </si>
+  <si>
     <t>testDATF</t>
   </si>
   <si>
@@ -277,9 +280,6 @@
   </si>
   <si>
     <t>dbfs:/databricks-datasets/sfo_customer_survey/</t>
-  </si>
-  <si>
-    <t>2013_SFO_Customer_Survey.CSV</t>
   </si>
 </sst>
 </file>
@@ -762,7 +762,7 @@
         <v>66</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -971,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>7</v>
@@ -983,7 +983,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>9</v>
@@ -995,10 +995,10 @@
         <v>15</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>7</v>
